--- a/artfynd/A 3294-2026 artfynd.xlsx
+++ b/artfynd/A 3294-2026 artfynd.xlsx
@@ -2106,7 +2106,7 @@
         <v>129423641</v>
       </c>
       <c r="B16" t="n">
-        <v>91620</v>
+        <v>91795</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2132,6 +2132,9 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åbytorp, Ryssjöbrink, Srm, Srm</t>
@@ -2178,7 +2181,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka fruktkroppar</t>
+          <t>Enstaka fruktkroppar I hällmarkstallskog &gt;150 år gammal med rikliga spridda förekomster</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2187,6 +2190,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3294-2026 artfynd.xlsx
+++ b/artfynd/A 3294-2026 artfynd.xlsx
@@ -2106,7 +2106,7 @@
         <v>129423641</v>
       </c>
       <c r="B16" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 3294-2026 artfynd.xlsx
+++ b/artfynd/A 3294-2026 artfynd.xlsx
@@ -2106,7 +2106,7 @@
         <v>129423641</v>
       </c>
       <c r="B16" t="n">
-        <v>91796</v>
+        <v>91797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 3294-2026 artfynd.xlsx
+++ b/artfynd/A 3294-2026 artfynd.xlsx
@@ -2106,7 +2106,7 @@
         <v>129423641</v>
       </c>
       <c r="B16" t="n">
-        <v>91797</v>
+        <v>91805</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 3294-2026 artfynd.xlsx
+++ b/artfynd/A 3294-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129423620</v>
+        <v>129423689</v>
       </c>
       <c r="B2" t="n">
-        <v>79700</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633445</v>
+        <v>633472</v>
       </c>
       <c r="R2" t="n">
-        <v>6565865</v>
+        <v>6565984</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Mindre förekomst</t>
+          <t>4 fruktkroppar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129423674</v>
+        <v>129423690</v>
       </c>
       <c r="B3" t="n">
-        <v>92919</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633446</v>
+        <v>633502</v>
       </c>
       <c r="R3" t="n">
-        <v>6565836</v>
+        <v>6565963</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Enstaka fruktkroppar</t>
+          <t>2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129423676</v>
+        <v>129423640</v>
       </c>
       <c r="B4" t="n">
-        <v>92919</v>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +890,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633460</v>
+        <v>633436</v>
       </c>
       <c r="R4" t="n">
-        <v>6565984</v>
+        <v>6565941</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129423675</v>
+        <v>129423641</v>
       </c>
       <c r="B5" t="n">
-        <v>92919</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +992,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Åbytorp, Ryssjöbrink, Srm, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633451</v>
+        <v>633458</v>
       </c>
       <c r="R5" t="n">
-        <v>6565964</v>
+        <v>6565966</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1056,7 +1059,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka fruktkroppar</t>
+          <t>Enstaka fruktkroppar I hällmarkstallskog &gt;150 år gammal med rikliga spridda förekomster</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1065,6 +1068,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1083,32 +1087,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129423689</v>
+        <v>129423642</v>
       </c>
       <c r="B6" t="n">
-        <v>92881</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1118,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633472</v>
+        <v>633537</v>
       </c>
       <c r="R6" t="n">
-        <v>6565984</v>
+        <v>6565965</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1158,7 +1162,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4 fruktkroppar</t>
+          <t>På gammal spärrgrenig tall. 2 fruktkroppar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129423621</v>
+        <v>129423674</v>
       </c>
       <c r="B7" t="n">
-        <v>79700</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1196,21 +1200,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1220,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633437</v>
+        <v>633446</v>
       </c>
       <c r="R7" t="n">
-        <v>6565978</v>
+        <v>6565836</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Mindre förekomst</t>
+          <t>Enstaka fruktkroppar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129423690</v>
+        <v>129423675</v>
       </c>
       <c r="B8" t="n">
-        <v>92881</v>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633502</v>
+        <v>633451</v>
       </c>
       <c r="R8" t="n">
-        <v>6565963</v>
+        <v>6565964</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1362,7 +1366,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2 fruktkroppar</t>
+          <t>Enstaka fruktkroppar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129423642</v>
+        <v>129423676</v>
       </c>
       <c r="B9" t="n">
-        <v>91620</v>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1400,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1424,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633537</v>
+        <v>633460</v>
       </c>
       <c r="R9" t="n">
-        <v>6565965</v>
+        <v>6565984</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1464,7 +1468,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal spärrgrenig tall. 2 fruktkroppar</t>
+          <t>Enstaka fruktkroppar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129423683</v>
+        <v>129423677</v>
       </c>
       <c r="B10" t="n">
-        <v>92919</v>
+        <v>93235</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633410</v>
+        <v>633510</v>
       </c>
       <c r="R10" t="n">
-        <v>6565888</v>
+        <v>6565963</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1566,7 +1570,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Två fruktkroppar</t>
+          <t>Enstaka fruktkroppar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129423677</v>
+        <v>129423678</v>
       </c>
       <c r="B11" t="n">
-        <v>92919</v>
+        <v>93235</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633510</v>
+        <v>633536</v>
       </c>
       <c r="R11" t="n">
-        <v>6565963</v>
+        <v>6565948</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129423678</v>
+        <v>129423682</v>
       </c>
       <c r="B12" t="n">
-        <v>92919</v>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1730,10 +1734,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633536</v>
+        <v>633545</v>
       </c>
       <c r="R12" t="n">
-        <v>6565948</v>
+        <v>6565951</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,10 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129423682</v>
+        <v>129423683</v>
       </c>
       <c r="B13" t="n">
-        <v>92919</v>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,10 +1836,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633545</v>
+        <v>633410</v>
       </c>
       <c r="R13" t="n">
-        <v>6565951</v>
+        <v>6565888</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1872,7 +1876,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Enstaka fruktkroppar</t>
+          <t>Två fruktkroppar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129423622</v>
+        <v>129423684</v>
       </c>
       <c r="B14" t="n">
-        <v>79700</v>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1910,21 +1914,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,10 +1938,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633376</v>
+        <v>633433</v>
       </c>
       <c r="R14" t="n">
-        <v>6565850</v>
+        <v>6565878</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1974,7 +1978,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Två mindre förekomster på solbelyst låga i hällmarktallskog</t>
+          <t>Två fruktkroppar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,10 +2005,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129423684</v>
+        <v>129423620</v>
       </c>
       <c r="B15" t="n">
-        <v>92919</v>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2012,21 +2016,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633433</v>
+        <v>633445</v>
       </c>
       <c r="R15" t="n">
-        <v>6565878</v>
+        <v>6565865</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2076,7 +2080,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Två fruktkroppar</t>
+          <t>Mindre förekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,10 +2107,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129423641</v>
+        <v>129423621</v>
       </c>
       <c r="B16" t="n">
-        <v>91829</v>
+        <v>79946</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2114,37 +2118,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Åbytorp, Ryssjöbrink, Srm, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633458</v>
+        <v>633437</v>
       </c>
       <c r="R16" t="n">
-        <v>6565966</v>
+        <v>6565978</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2181,7 +2182,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka fruktkroppar I hällmarkstallskog &gt;150 år gammal med rikliga spridda förekomster</t>
+          <t>Mindre förekomst</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2190,7 +2191,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2209,10 +2209,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129423650</v>
+        <v>129423622</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2220,39 +2220,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Åbytorp, Ryssjöbrink, Srm, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633362</v>
+        <v>633376</v>
       </c>
       <c r="R17" t="n">
-        <v>6565878</v>
+        <v>6565850</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2289,7 +2284,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Födosökspår</t>
+          <t>Två mindre förekomster på solbelyst låga i hällmarktallskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2319,11 +2314,11 @@
         <v>129423648</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2426,11 +2421,11 @@
         <v>129423649</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2530,45 +2525,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129423640</v>
+        <v>129423650</v>
       </c>
       <c r="B20" t="n">
-        <v>91620</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Åbytorp, Ryssjöbrink, Srm, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633436</v>
+        <v>633362</v>
       </c>
       <c r="R20" t="n">
-        <v>6565941</v>
+        <v>6565878</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Enstaka fruktkroppar</t>
+          <t>Födosökspår</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 3294-2026 artfynd.xlsx
+++ b/artfynd/A 3294-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423689</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423690</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423640</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423641</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423642</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423674</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423675</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423676</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423677</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1696,6 +1746,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423678</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423682</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1900,6 +1960,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423683</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2002,6 +2067,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423684</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2104,6 +2174,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423620</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2206,6 +2281,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423621</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2308,6 +2388,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423622</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2415,6 +2500,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423648</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2522,6 +2612,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423649</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2629,8 +2724,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129423650</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>